--- a/ig/DM-JUIN-2026/ValueSet-jdv-type-intervention-voie-basse-cisis.xlsx
+++ b/ig/DM-JUIN-2026/ValueSet-jdv-type-intervention-voie-basse-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150249</t>
+    <t>20260619134041</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:49+01:00</t>
+    <t>2026-06-19T13:40:41+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
